--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$12</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$15</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="42">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -122,6 +122,33 @@
   </si>
   <si>
     <t xml:space="preserve">Утверждён, включён в Release 1.0 FOUNDATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оператор ИИ-агентов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Добавлен Режим Б: автономный подбор оборудования и параметров ChatGPT по открытым данным (ГОСТ/типовые каталоги), с обязательной пометкой и проверкой эксперта перед утверждением</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Добавлен Режим Б: автономный подбор узла оборудования и типового регламента ChatGPT по открытым данным, с обязательной пометкой и проверкой специалистом по ОТ перед утверждением</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Добавлен Режим Б: автономный подбор типовой операции ChatGPT по открытой отраслевой практике, с обязательной пометкой и проверкой эксперта перед утверждением</t>
   </si>
 </sst>
 </file>
@@ -232,8 +259,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -526,222 +557,273 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="55"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="3" t="s">
         <v>32</v>
       </c>
     </row>
+    <row r="13" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E12"/>
+  <autoFilter ref="A1:E15"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$15</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$19</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="48">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -149,6 +149,24 @@
   </si>
   <si>
     <t xml:space="preserve">Добавлен Режим Б: автономный подбор типовой операции ChatGPT по открытой отраслевой практике, с обязательной пометкой и проверкой эксперта перед утверждением</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СТД-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ИИ (ChatGPT, Режим Б) + Claude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Черновик сформирован по открытым данным (типовые параметры водогрейных котлов), промпты ПРМ-001/ПРМ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Утверждён с пометкой о необходимости привязки типовых значений к фактическому оборудованию объекта; включён в структуру раздела</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СТД-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Черновик сформирован по открытым данным (типовые параметры циркуляционных насосов), промпты ПРМ-001/ПРМ-002</t>
   </si>
 </sst>
 </file>
@@ -557,7 +575,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -788,7 +806,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
@@ -805,7 +823,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
@@ -822,8 +840,76 @@
         <v>41</v>
       </c>
     </row>
+    <row r="16" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E15"/>
+  <autoFilter ref="A1:E19"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$19</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$22</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="56">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -167,6 +167,30 @@
   </si>
   <si>
     <t xml:space="preserve">Черновик сформирован по открытым данным (типовые параметры циркуляционных насосов), промпты ПРМ-001/ПРМ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РГЛ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ИИ (ChatGPT, Режим Б)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Черновик сформирован по открытым данным (типовая периодичность обслуживания теплообменных аппаратов), промпт ПРМ-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактор раздела 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Утверждён с пометкой о необходимости проверки специалистом по ОТ и привязки к фактическому оборудованию объекта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ИНС-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Черновик сформирован по открытой отраслевой практике (промпт ПРМ-005). Раздел «Типичные ошибки» намеренно оставлен незаполненным — требует реального опыта эксплуатации перед переводом в статус «Утверждено»</t>
   </si>
 </sst>
 </file>
@@ -575,7 +599,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -840,7 +864,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
         <v>42</v>
       </c>
@@ -857,7 +881,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
         <v>42</v>
       </c>
@@ -874,7 +898,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>46</v>
       </c>
@@ -891,7 +915,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
         <v>46</v>
       </c>
@@ -908,8 +932,59 @@
         <v>45</v>
       </c>
     </row>
+    <row r="20" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E19"/>
+  <autoFilter ref="A1:E22"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$22</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$29</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="67">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -191,6 +191,39 @@
   </si>
   <si>
     <t xml:space="preserve">Черновик сформирован по открытой отраслевой практике (промпт ПРМ-005). Раздел «Типичные ошибки» намеренно оставлен незаполненным — требует реального опыта эксплуатации перед переводом в статус «Утверждено»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЭНЦ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ИИ (ChatGPT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Черновик и утверждение — теория теплопередачи, обоснование признаков отклонений СТД-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЭНЦ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Черновик и утверждение — теория горения и КПД, обоснование признаков отклонений СТД-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЭНЦ-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Черновик и утверждение — теория центробежных насосов, обоснование признаков отклонений СТД-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Добавлена перекрёстная ссылка на ЭНЦ-001 в раздел «Ссылки»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Добавлена перекрёстная ссылка на ЭНЦ-002 в раздел «Ссылки»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Добавлена перекрёстная ссылка на ЭНЦ-003 в раздел «Ссылки»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Добавлена перекрёстная ссылка на ЭНЦ-001 в раздел «Область применения»</t>
   </si>
 </sst>
 </file>
@@ -599,7 +632,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -966,7 +999,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
         <v>53</v>
       </c>
@@ -983,8 +1016,127 @@
         <v>55</v>
       </c>
     </row>
+    <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E22"/>
+  <autoFilter ref="A1:E29"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$29</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$35</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="74">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -224,6 +224,27 @@
   </si>
   <si>
     <t xml:space="preserve">Добавлена перекрёстная ссылка на ЭНЦ-001 в раздел «Область применения»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сформирован и утверждён на основе соответствующего утверждённого документа (промпт ПРМ-008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-006</t>
   </si>
 </sst>
 </file>
@@ -632,7 +653,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -1016,7 +1037,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
         <v>56</v>
       </c>
@@ -1033,7 +1054,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>59</v>
       </c>
@@ -1050,7 +1071,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
         <v>61</v>
       </c>
@@ -1067,7 +1088,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -1084,7 +1105,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
         <v>42</v>
       </c>
@@ -1101,7 +1122,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
         <v>46</v>
       </c>
@@ -1118,7 +1139,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
         <v>48</v>
       </c>
@@ -1135,8 +1156,110 @@
         <v>66</v>
       </c>
     </row>
+    <row r="30" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E29"/>
+  <autoFilter ref="A1:E35"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$35</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$45</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="86">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -245,6 +245,42 @@
   </si>
   <si>
     <t xml:space="preserve">FAQ-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сформирована и утверждена промптом ПРМ-009 на основе соответствующего документа-источника</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0010</t>
   </si>
 </sst>
 </file>
@@ -653,7 +689,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -1156,7 +1192,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
         <v>67</v>
       </c>
@@ -1173,7 +1209,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
         <v>69</v>
       </c>
@@ -1190,7 +1226,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
         <v>70</v>
       </c>
@@ -1207,7 +1243,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
         <v>71</v>
       </c>
@@ -1224,7 +1260,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
         <v>72</v>
       </c>
@@ -1241,7 +1277,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
         <v>73</v>
       </c>
@@ -1258,8 +1294,178 @@
         <v>68</v>
       </c>
     </row>
+    <row r="36" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E35"/>
+  <autoFilter ref="A1:E45"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$45</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$46</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="89">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -281,6 +281,15 @@
   </si>
   <si>
     <t xml:space="preserve">RAG-0010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НСП-Каталог</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактор раздела 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Собраны 7 неисправностей, ранее упоминавшихся по названию в СТД-001/002/003, ЭНЦ-001/002/003 и RAG-карточках, без единого места хранения</t>
   </si>
 </sst>
 </file>
@@ -689,7 +698,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -1294,7 +1303,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
         <v>74</v>
       </c>
@@ -1311,7 +1320,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>77</v>
       </c>
@@ -1328,7 +1337,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>78</v>
       </c>
@@ -1345,7 +1354,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>79</v>
       </c>
@@ -1362,7 +1371,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>80</v>
       </c>
@@ -1379,7 +1388,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
         <v>81</v>
       </c>
@@ -1396,7 +1405,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
         <v>82</v>
       </c>
@@ -1413,7 +1422,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
         <v>83</v>
       </c>
@@ -1430,7 +1439,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
         <v>84</v>
       </c>
@@ -1447,7 +1456,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
         <v>85</v>
       </c>
@@ -1464,8 +1473,25 @@
         <v>76</v>
       </c>
     </row>
+    <row r="46" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E45"/>
+  <autoFilter ref="A1:E46"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$46</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$48</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="93">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -290,6 +290,18 @@
   </si>
   <si>
     <t xml:space="preserve">Собраны 7 неисправностей, ранее упоминавшихся по названию в СТД-001/002/003, ЭНЦ-001/002/003 и RAG-карточках, без единого места хранения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РЕШ-Каталог</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактор раздела 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Собраны 7 типовых решений, каждое устраняет конкретную неисправность из 10_Каталог_неисправностей (соответствие 1:1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Колонка «Типовое решение» обновлена точными ссылками на коды РЕШ-001…РЕШ-007 вместо текстовой заглушки</t>
   </si>
 </sst>
 </file>
@@ -698,7 +710,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -1473,7 +1485,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
         <v>86</v>
       </c>
@@ -1490,8 +1502,42 @@
         <v>88</v>
       </c>
     </row>
+    <row r="47" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E46"/>
+  <autoFilter ref="A1:E48"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$48</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$52</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="102">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -302,6 +302,33 @@
   </si>
   <si>
     <t xml:space="preserve">Колонка «Типовое решение» обновлена точными ссылками на коды РЕШ-001…РЕШ-007 вместо текстовой заглушки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ШБ-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактор раздела 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Новый шаблон карточки оборудования — отсутствовал в исходном комплекте ШБ-001…008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КАР-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пример заполнения по СТД-001/РГЛ-001/ЭНЦ-001, типовые данные, требует замены на реальные при вводе единицы оборудования</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КАР-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пример заполнения по СТД-002/ЭНЦ-002, типовые данные</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КАР-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пример заполнения по СТД-003/ИНС-001/ЭНЦ-003, типовые данные</t>
   </si>
 </sst>
 </file>
@@ -710,7 +737,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -1502,7 +1529,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
         <v>89</v>
       </c>
@@ -1519,7 +1546,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
         <v>86</v>
       </c>
@@ -1536,8 +1563,76 @@
         <v>92</v>
       </c>
     </row>
+    <row r="49" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E48"/>
+  <autoFilter ref="A1:E52"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$52</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$54</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="106">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -329,6 +329,18 @@
   </si>
   <si>
     <t xml:space="preserve">Пример заполнения по СТД-003/ИНС-001/ЭНЦ-003, типовые данные</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КЕЙС-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Иллюстративный пример по цепочке СТД-001 → НСП-001 → РЕШ-001, не привязан к реальному объекту</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КЕЙС-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Иллюстративный пример по цепочке ИНС-001 → СТД-003 → НСП-005 → РЕШ-005, кандидат материала для «Типичные ошибки» ИНС-001</t>
   </si>
 </sst>
 </file>
@@ -737,7 +749,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -1563,7 +1575,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
         <v>93</v>
       </c>
@@ -1580,7 +1592,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
         <v>96</v>
       </c>
@@ -1597,7 +1609,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
         <v>98</v>
       </c>
@@ -1614,7 +1626,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
         <v>100</v>
       </c>
@@ -1631,8 +1643,42 @@
         <v>101</v>
       </c>
     </row>
+    <row r="53" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E52"/>
+  <autoFilter ref="A1:E54"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$54</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$57</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="110">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -341,6 +341,18 @@
   </si>
   <si>
     <t xml:space="preserve">Иллюстративный пример по цепочке ИНС-001 → СТД-003 → НСП-005 → РЕШ-005, кандидат материала для «Типичные ошибки» ИНС-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Удалена дублирующая ссылка на пустой 11_Физика_процессов (нарушение принципа единственного источника истины, КП-001); оставлена конкретная ссылка на ЭНЦ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аналогично — удалена дублирующая ссылка на 11_Физика_процессов, оставлена ссылка на ЭНЦ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аналогично — удалена дублирующая ссылка на 11_Физика_процессов, оставлена ссылка на ЭНЦ-003</t>
   </si>
 </sst>
 </file>
@@ -749,7 +761,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -1643,7 +1655,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
         <v>102</v>
       </c>
@@ -1660,7 +1672,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
         <v>104</v>
       </c>
@@ -1677,8 +1689,59 @@
         <v>105</v>
       </c>
     </row>
+    <row r="55" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E54"/>
+  <autoFilter ref="A1:E57"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$57</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$65</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="120">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -353,6 +353,36 @@
   </si>
   <si>
     <t xml:space="preserve">Аналогично — удалена дублирующая ссылка на 11_Физика_процессов, оставлена ссылка на ЭНЦ-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">АУДИТ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claude (самоаудит)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сквозной аудит всего проекта: найдены и исправлены битые ссылки RAG-0001…0006 на устаревшую версию СТД (после повышения СТД до v1.2), устранена дублирующая ссылка на теорию</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Исправлена битая ссылка на источник: путь и версия обновлены на СТД-001 v1.2 (была v1.1, файл больше не существовал)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аналогично RAG-0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Исправлена битая ссылка на источник: путь и версия обновлены на СТД-002 v1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аналогично RAG-0003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Исправлена битая ссылка на источник: путь и версия обновлены на СТД-003 v1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аналогично RAG-0005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Первый формальный сквозной аудит проекта по логике ПРМ-011, оформлен по шаблону ШБ-007</t>
   </si>
 </sst>
 </file>
@@ -761,7 +791,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -1689,7 +1719,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
         <v>28</v>
       </c>
@@ -1706,7 +1736,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
         <v>42</v>
       </c>
@@ -1723,7 +1753,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
         <v>46</v>
       </c>
@@ -1740,8 +1770,144 @@
         <v>109</v>
       </c>
     </row>
+    <row r="58" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E57"/>
+  <autoFilter ref="A1:E65"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$65</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$68</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="128">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -383,6 +383,30 @@
   </si>
   <si>
     <t xml:space="preserve">Первый формальный сквозной аудит проекта по логике ПРМ-011, оформлен по шаблону ШБ-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СЛВ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактор раздела 09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Читаемое представление Реестра_терминов.xlsx (14 терминов); добавлено 8 новых терминов, встречавшихся в СТД/ЭНЦ/РГЛ, но ранее не зафиксированных в реестре</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Добавлено 15 терминов, сверенных с ФЗ №190-ФЗ, ГОСТ 22270-2018, СП 124.13330.2012; всего терминов — 29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НД-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактор раздела 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Индекс 3 внешних нормативных документов, используемых для терминологии проекта; полный текст не воспроизводится</t>
   </si>
 </sst>
 </file>
@@ -791,7 +815,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -1889,7 +1913,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
         <v>110</v>
       </c>
@@ -1906,8 +1930,59 @@
         <v>119</v>
       </c>
     </row>
+    <row r="66" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E65"/>
+  <autoFilter ref="A1:E68"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$68</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$72</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="135">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -407,6 +407,27 @@
   </si>
   <si>
     <t xml:space="preserve">Индекс 3 внешних нормативных документов, используемых для терминологии проекта; полный текст не воспроизводится</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактор раздела 03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В раздел «Типичные ошибки» добавлена одна запись, явно помеченная как иллюстративная (источник — иллюстративный кейс КЕЙС-002, не реальный опыт эксплуатации). Статус остаётся «На редакции» — документ по-прежнему не может быть утверждён без записи реального опыта эксплуатации персонала (см. КП-002)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Исправлена ссылка на источник (ИНС-001 v0.9 → v0.91) сразу при повышении версии источника — предотвращение повторения проблемы, найденной АУДИТ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Утверждён. Раздел «Типичные ошибки» заполнен 6 документированными отраслевыми случаями из открытых источников (реальные инциденты, предоставлены пользователем). Документ перемещён из 20_На_редакции в 03_Инструкции_ИНС по статусной модели КП-007. Разделы 2-3 дополнены явными ссылками на случаи из раздела 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обновлён источник (ИНС-001 v1.0, статус «Утверждено»), убрана оговорка о черновом статусе источника</t>
   </si>
 </sst>
 </file>
@@ -815,7 +836,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -1947,7 +1968,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
         <v>120</v>
       </c>
@@ -1964,7 +1985,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
         <v>125</v>
       </c>
@@ -1981,8 +2002,76 @@
         <v>127</v>
       </c>
     </row>
+    <row r="69" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E68"/>
+  <autoFilter ref="A1:E72"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$72</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$73</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="137">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -428,6 +428,12 @@
   </si>
   <si>
     <t xml:space="preserve">Обновлён источник (ИНС-001 v1.0, статус «Утверждено»), убрана оговорка о черновом статусе источника</t>
+  </si>
+  <si>
+    <t xml:space="preserve">АРХ-Журнал</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обнаружено нарушение КП-005: 9 устаревших версий документов удалялись вместо архивирования. Восстановлены из истории git и размещены в 25_Архив с журналом</t>
   </si>
 </sst>
 </file>
@@ -836,7 +842,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -2036,7 +2042,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
         <v>53</v>
       </c>
@@ -2053,7 +2059,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
         <v>85</v>
       </c>
@@ -2070,8 +2076,25 @@
         <v>134</v>
       </c>
     </row>
+    <row r="73" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E72"/>
+  <autoFilter ref="A1:E73"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$73</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$75</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="141">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -434,6 +434,18 @@
   </si>
   <si>
     <t xml:space="preserve">Обнаружено нарушение КП-005: 9 устаревших версий документов удалялись вместо архивирования. Восстановлены из истории git и размещены в 25_Архив с журналом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0 (исправление)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Устранена дублирующая запись в Реестре документов (техническая ошибка регистрации, не изменение содержания самого документа)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RELEASE-1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Формальный релиз, консолидирующий все изменения с момента Release 1.0 FOUNDATION (18 рабочих итераций). Утверждён Владельцем Проекта. В папку релиза добавлены замороженные снимки MANIFEST.xlsx и Реестра_документов.xlsx на дату релиза</t>
   </si>
 </sst>
 </file>
@@ -842,7 +854,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -2076,7 +2088,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
         <v>135</v>
       </c>
@@ -2093,8 +2105,42 @@
         <v>136</v>
       </c>
     </row>
+    <row r="74" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E73"/>
+  <autoFilter ref="A1:E75"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$75</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$84</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="151">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -446,6 +446,36 @@
   </si>
   <si>
     <t xml:space="preserve">Формальный релиз, консолидирующий все изменения с момента Release 1.0 FOUNDATION (18 рабочих итераций). Утверждён Владельцем Проекта. В папку релиза добавлены замороженные снимки MANIFEST.xlsx и Реестра_документов.xlsx на дату релиза</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РГЛ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сформирован по открытым данным, промпт ПРМ-003 (аналогично РГЛ-001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РГЛ-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сформирован по открытым данным, промпт ПРМ-003; ссылается на ИНС-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Добавлена ссылка на новый РГЛ-002 в разделе «Ссылки»; старая v1.2 перенесена в 25_Архив/2026-07-11_v1.2_to_v1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Добавлены ссылки на новый РГЛ-003 и ИНС-001 в разделе «Ссылки»; старая v1.2 перенесена в 25_Архив/2026-07-11_v1.2_to_v1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактор раздела 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Добавлены 2 записи: СТД-002/003 v1.2 архивированы при переходе на v1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обновлён путь/версия источника вслед за СТД v1.2→v1.3 (проверено сразу при повышении версии источника)</t>
   </si>
 </sst>
 </file>
@@ -854,7 +884,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -2105,7 +2135,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
         <v>110</v>
       </c>
@@ -2122,7 +2152,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
         <v>139</v>
       </c>
@@ -2139,8 +2169,161 @@
         <v>140</v>
       </c>
     </row>
+    <row r="76" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E75"/>
+  <autoFilter ref="A1:E84"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$84</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$103</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="175">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -476,6 +476,78 @@
   </si>
   <si>
     <t xml:space="preserve">Обновлён путь/версия источника вслед за СТД v1.2→v1.3 (проверено сразу при повышении версии источника)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ШБ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Создан в составе первоначального комплекта шаблонов (Release 1.0 FOUNDATION); запись добавлена задним числом при аудите АУДИТ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ШБ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ШБ-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ШБ-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ШБ-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ШБ-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ШБ-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ШБ-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Создан в составе первого пакета промптов (Release 1.1 наполнение 07_Промпты); запись добавлена задним числом при аудите АУДИТ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Создан в составе первого пакета промптов; запись добавлена задним числом при аудите АУДИТ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">АУДИТ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claude (по поручению Владельца Проекта)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Второй формальный сквозной аудит: найдено и исправлено 4 замечания (дубль в реестре, неполные кросс-ссылки в каталоге неисправностей, 18 недорегистрированных документов, дублирующий блок в CHANGELOG)</t>
   </si>
 </sst>
 </file>
@@ -884,7 +956,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -2254,7 +2326,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
         <v>78</v>
       </c>
@@ -2271,7 +2343,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
         <v>79</v>
       </c>
@@ -2288,7 +2360,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
         <v>80</v>
       </c>
@@ -2305,7 +2377,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
         <v>81</v>
       </c>
@@ -2322,8 +2394,331 @@
         <v>150</v>
       </c>
     </row>
+    <row r="85" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E84"/>
+  <autoFilter ref="A1:E103"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$103</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$108</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="183">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -548,6 +548,30 @@
   </si>
   <si>
     <t xml:space="preserve">Второй формальный сквозной аудит: найдено и исправлено 4 замечания (дубль в реестре, неполные кросс-ссылки в каталоге неисправностей, 18 недорегистрированных документов, дублирующий блок в CHANGELOG)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сформирована и утверждена промптом ПРМ-009 на основе РГЛ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сформирована и утверждена промптом ПРМ-009 на основе РГЛ-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КЕЙС-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Иллюстративный пример по цепочке СТД-002 → НСП-002 → РЕШ-002, не привязан к реальному объекту; закрывает пробел — единственный тип оборудования без кейса</t>
   </si>
 </sst>
 </file>
@@ -956,7 +980,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -2700,7 +2724,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="3" t="s">
         <v>172</v>
       </c>
@@ -2717,8 +2741,93 @@
         <v>174</v>
       </c>
     </row>
+    <row r="104" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E103"/>
+  <autoFilter ref="A1:E108"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$108</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$124</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="208">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -572,6 +572,81 @@
   </si>
   <si>
     <t xml:space="preserve">Иллюстративный пример по цепочке СТД-002 → НСП-002 → РЕШ-002, не привязан к реальному объекту; закрывает пробел — единственный тип оборудования без кейса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СТД-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Черновик и утверждение — диагностика электрических котлов (ТЭН/электродного типа), промпты ПРМ-001/ПРМ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СТД-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Черновик и утверждение — диагностика твердотопливных котлов, промпты ПРМ-001/ПРМ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РГЛ-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сформирован по открытым данным, промпт ПРМ-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РГЛ-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЭНЦ-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Теория ТЭН и накипеобразования, обоснование признаков отклонений СТД-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЭНЦ-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Теория горения твёрдого топлива и тяги, обоснование признаков отклонений СТД-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сформирована промптом ПРМ-009 на основе СТД-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сформирована промптом ПРМ-009 на основе СТД-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сформирована промптом ПРМ-009 на основе РГЛ-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Добавлено 4 термина (ТЭН, колосниковая решётка, тяга, зашлаковывание) для новых типов котлов; всего 33 термина</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Добавлены НСП-008…011 (накипь на ТЭН, утечка тока, зашлаковывание решётки, недостаточная тяга) для электрических и твердотопливных котлов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Добавлены РЕШ-008…011, соответствующие новым неисправностям НСП-008…011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Добавлена перекрёстная ссылка на новые СТД-004 (электрические котлы) и СТД-005 (твердотопливные котлы); старая v1.3 перенесена в 25_Архив/2026-07-12_v1.3_to_v1.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обновлён путь/версия источника вслед за СТД-002 v1.3→v1.4 (проверено сразу)</t>
   </si>
 </sst>
 </file>
@@ -687,15 +762,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -980,7 +1055,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E124"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -2741,7 +2816,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="3" t="s">
         <v>175</v>
       </c>
@@ -2758,7 +2833,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="3" t="s">
         <v>177</v>
       </c>
@@ -2775,7 +2850,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="s">
         <v>178</v>
       </c>
@@ -2792,7 +2867,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="3" t="s">
         <v>180</v>
       </c>
@@ -2809,7 +2884,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="s">
         <v>181</v>
       </c>
@@ -2826,8 +2901,280 @@
         <v>182</v>
       </c>
     </row>
+    <row r="109" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E108"/>
+  <autoFilter ref="A1:E124"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$124</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$128</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="216">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -647,6 +647,30 @@
   </si>
   <si>
     <t xml:space="preserve">Обновлён путь/версия источника вслед за СТД-002 v1.3→v1.4 (проверено сразу)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КАР-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пример заполнения по СТД-004/РГЛ-004/ЭНЦ-004, типовые данные</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КАР-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пример заполнения по СТД-005/РГЛ-005/ЭНЦ-005, типовые данные</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КЕЙС-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Иллюстративный пример по цепочке СТД-004 → НСП-008 → РЕШ-008, не привязан к реальному объекту</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КЕЙС-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Иллюстративный пример по цепочке СТД-005 → НСП-010 → РЕШ-010, не привязан к реальному объекту</t>
   </si>
 </sst>
 </file>
@@ -762,15 +786,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1055,7 +1079,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E124"/>
+  <dimension ref="A1:E128"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -3122,7 +3146,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="3" t="s">
         <v>42</v>
       </c>
@@ -3139,7 +3163,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="3" t="s">
         <v>78</v>
       </c>
@@ -3156,7 +3180,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="s">
         <v>79</v>
       </c>
@@ -3173,8 +3197,76 @@
         <v>207</v>
       </c>
     </row>
+    <row r="125" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E124"/>
+  <autoFilter ref="A1:E128"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$128</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$138</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="228">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -671,6 +671,42 @@
   </si>
   <si>
     <t xml:space="preserve">Иллюстративный пример по цепочке СТД-005 → НСП-010 → РЕШ-010, не привязан к реальному объекту</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-К-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Первый черновик клиентского FAQ, написан для конечного потребителя (не персонала); требует проверки ответственным лицом и заполнения плейсхолдеров контактов перед публикацией на сайте</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-К-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-К-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-К-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-К-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-К-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-К-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-К-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-К-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-К-010</t>
   </si>
 </sst>
 </file>
@@ -1079,7 +1115,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E128"/>
+  <dimension ref="A1:E138"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -3197,7 +3233,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="3" t="s">
         <v>208</v>
       </c>
@@ -3214,7 +3250,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="s">
         <v>210</v>
       </c>
@@ -3231,7 +3267,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="3" t="s">
         <v>212</v>
       </c>
@@ -3248,7 +3284,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="s">
         <v>214</v>
       </c>
@@ -3265,8 +3301,178 @@
         <v>215</v>
       </c>
     </row>
+    <row r="129" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E128"/>
+  <autoFilter ref="A1:E138"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$138</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$166</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="260">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -707,6 +707,102 @@
   </si>
   <si>
     <t xml:space="preserve">FAQ-К-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЧД-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Первый черновик клиентского FAQ для сегмента «Частные_дома», требует проверки ответственным лицом и заполнения плейсхолдеров перед публикацией</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЧД-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЧД-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЧД-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЧД-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЧД-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЧД-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЧД-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-УК-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Первый черновик клиентского FAQ для сегмента «УК_ЖКХ», требует проверки ответственным лицом и заполнения плейсхолдеров перед публикацией</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-УК-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-УК-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-УК-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-УК-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-УК-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-УК-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-УК-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЮЛ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Первый черновик клиентского FAQ для сегмента «Юрлица», требует проверки ответственным лицом и заполнения плейсхолдеров перед публикацией</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЮЛ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЮЛ-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЮЛ-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЮЛ-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЮЛ-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ИНФ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Первый черновик клиентского FAQ для сегмента «Инфраструктура_ГВС», требует проверки ответственным лицом и заполнения плейсхолдеров перед публикацией</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ИНФ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ИНФ-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ИНФ-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ИНФ-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ИНФ-006</t>
   </si>
 </sst>
 </file>
@@ -1115,7 +1211,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:E166"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -3301,7 +3397,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="3" t="s">
         <v>216</v>
       </c>
@@ -3318,7 +3414,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="3" t="s">
         <v>219</v>
       </c>
@@ -3335,7 +3431,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="3" t="s">
         <v>220</v>
       </c>
@@ -3352,7 +3448,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="3" t="s">
         <v>221</v>
       </c>
@@ -3369,7 +3465,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="3" t="s">
         <v>222</v>
       </c>
@@ -3386,7 +3482,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
         <v>223</v>
       </c>
@@ -3403,7 +3499,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="3" t="s">
         <v>224</v>
       </c>
@@ -3420,7 +3516,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="s">
         <v>225</v>
       </c>
@@ -3437,7 +3533,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="s">
         <v>226</v>
       </c>
@@ -3454,7 +3550,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
         <v>227</v>
       </c>
@@ -3471,8 +3567,484 @@
         <v>218</v>
       </c>
     </row>
+    <row r="139" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E138"/>
+  <autoFilter ref="A1:E166"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_версий.xlsx
+++ b/00_Проект/02_Реестр/Реестр_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$166</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр версий'!$A$1:$E$167</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="262">
   <si>
     <t xml:space="preserve">Документ (код)</t>
   </si>
@@ -803,6 +803,12 @@
   </si>
   <si>
     <t xml:space="preserve">FAQ-ИНФ-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЧЕК-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Составлен путём сканирования всех 38 клиентских FAQ на плейсхолдеры; классифицирован по приоритету (критично/особый/высокий/средний/низкий)</t>
   </si>
 </sst>
 </file>
@@ -1211,7 +1217,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E166"/>
+  <dimension ref="A1:E167"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -3567,7 +3573,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="s">
         <v>228</v>
       </c>
@@ -3584,7 +3590,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
         <v>230</v>
       </c>
@@ -3601,7 +3607,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="s">
         <v>231</v>
       </c>
@@ -3618,7 +3624,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="s">
         <v>232</v>
       </c>
@@ -3635,7 +3641,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="3" t="s">
         <v>233</v>
       </c>
@@ -3652,7 +3658,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
         <v>234</v>
       </c>
@@ -3669,7 +3675,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
         <v>235</v>
       </c>
@@ -3686,7 +3692,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="s">
         <v>236</v>
       </c>
@@ -3703,7 +3709,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="3" t="s">
         <v>237</v>
       </c>
@@ -3720,7 +3726,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
         <v>239</v>
       </c>
@@ -3737,7 +3743,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
         <v>240</v>
       </c>
@@ -3754,7 +3760,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="s">
         <v>241</v>
       </c>
@@ -3771,7 +3777,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="3" t="s">
         <v>242</v>
       </c>
@@ -3788,7 +3794,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
         <v>243</v>
       </c>
@@ -3805,7 +3811,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="s">
         <v>244</v>
       </c>
@@ -3822,7 +3828,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
         <v>245</v>
       </c>
@@ -3839,7 +3845,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="3" t="s">
         <v>246</v>
       </c>
@@ -3856,7 +3862,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="3" t="s">
         <v>248</v>
       </c>
@@ -3873,7 +3879,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="3" t="s">
         <v>249</v>
       </c>
@@ -3890,7 +3896,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
         <v>250</v>
       </c>
@@ -3907,7 +3913,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="3" t="s">
         <v>251</v>
       </c>
@@ -3924,7 +3930,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="s">
         <v>252</v>
       </c>
@@ -3941,7 +3947,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="3" t="s">
         <v>253</v>
       </c>
@@ -3958,7 +3964,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
         <v>255</v>
       </c>
@@ -3975,7 +3981,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="3" t="s">
         <v>256</v>
       </c>
@@ -3992,7 +3998,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="s">
         <v>257</v>
       </c>
@@ -4009,7 +4015,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="s">
         <v>258</v>
       </c>
@@ -4026,7 +4032,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="s">
         <v>259</v>
       </c>
@@ -4043,8 +4049,25 @@
         <v>254</v>
       </c>
     </row>
+    <row r="167" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E166"/>
+  <autoFilter ref="A1:E167"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
